--- a/sample_data/fixed_data/fix_list.xlsx
+++ b/sample_data/fixed_data/fix_list.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="待修改清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="__ecommerce_checker__" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,40 +414,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>商品编码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>商品标题</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>错误信息</t>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>问题数量</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>待修改内容</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>修复建议</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>PROD002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>假数据</t>
+          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>这是模拟报告文件，不应被读取</t>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>- title: 标题长度为 160 字符，超过最大限制 60 字符
+- detail_images: 详情图数量不足，当前 2 张，建议至少3张</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>- 请精简标题至 60 字符以内
+- 请补充更多详情图以展示商品细节</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>高仿奢侈品包包原单复刻</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>- title: 标题包含敏感词: 爆款
+- main_image: 缺少商品主图
+- detail_images: 缺少商品详情图</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>- 请删除或替换敏感词
+- 请在 images 目录下添加 PROD003_main.jpg 或 PROD003.jpg 作为主图
+- 请在 images 目录下添加 PROD003_detail_1.jpg, PROD003_detail_2.jpg 等详情图</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- title: 商品标题为空
+- stock: 商品库存为0
+- main_image: 缺少商品主图
+- detail_images: 缺少商品详情图</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>- 请填写商品标题
+- 请确认是否需要补充库存
+- 请在 images 目录下添加 PROD004_main.jpg 或 PROD004.jpg 作为主图
+- 请在 images 目录下添加 PROD004_detail_1.jpg, PROD004_detail_2.jpg 等详情图</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PROD005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>纯棉T恤夏季新款短袖</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- price: 价格 -10.0 超出合理区间 [0.1, 999999]
+- stock: 库存数量为负数: -5
+- main_image: 缺少商品主图
+- detail_images: 缺少商品详情图
+- category: 商品类目为空</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>- 请确认价格是否在 0.1 - 999999 范围内
+- 请填写非负的库存数量
+- 请在 images 目录下添加 PROD005_main.jpg 或 PROD005.jpg 作为主图
+- 请在 images 目录下添加 PROD005_detail_1.jpg, PROD005_detail_2.jpg 等详情图
+- 建议类目: 服装</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PROD006</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>运动鞋轻便透气跑步鞋</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>- stock: 库存数量为负数: -100
+- detail_images: 详情图数量不足，当前 1 张，建议至少3张</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>- 请填写非负的库存数量
+- 请补充更多详情图以展示商品细节</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ecommerce_checker_tool_generated</t>
         </is>
       </c>
     </row>

--- a/sample_data/fixed_data/fix_list.xlsx
+++ b/sample_data/fixed_data/fix_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个</t>
+          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,13 +470,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>- title: 标题长度为 160 字符，超过最大限制 60 字符
-- detail_images: 详情图数量不足，当前 2 张，建议至少3张</t>
+          <t>- title: 标题长度为 160 字符，超过最大限制 50 字符
+- detail_images: 详情图数量不足，当前 2 张，建议至少 5 张</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>- 请精简标题至 60 字符以内
+          <t>- 请精简标题至 50 字符以内
 - 请补充更多详情图以展示商品细节</t>
         </is>
       </c>
@@ -502,7 +502,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>- title: 标题包含敏感词: 爆款
+          <t>- title: 标题包含敏感词: 爆款, 爆款
 - main_image: 缺少商品主图
 - detail_images: 缺少商品详情图</t>
         </is>
@@ -607,13 +607,143 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>- stock: 库存数量为负数: -100
-- detail_images: 详情图数量不足，当前 1 张，建议至少3张</t>
+- detail_images: 详情图数量不足，当前 1 张，建议至少 3 张</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>- 请填写非负的库存数量
 - 请补充更多详情图以展示商品细节</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PROD007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>纯棉衬衫商务休闲长袖</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>- 详情图1: 详情图1文件不存在: sample_data\images\PROD007_detail_1.jpg
+- 详情图2: 详情图2文件不存在: sample_data\images\PROD007_detail_2.jpg
+- 详情图3: 详情图3文件不存在: sample_data\images\PROD007_detail_3.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>- 请检查图片路径是否正确，确保图片文件存在
+- 请检查图片路径是否正确，确保图片文件存在
+- 请检查图片路径是否正确，确保图片文件存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PROD008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小尺寸图片测试商品</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>- 主图: 主图尺寸过小: 400x400，建议不小于 1000x1000
+- 详情图1: 详情图1尺寸过小: 600x600，建议不小于 1000x1000
+- detail_images: 详情图数量不足，当前 1 张，建议至少 5 张</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>- 请使用更高分辨率的图片以保证展示效果
+- 请使用更高分辨率的图片以保证展示效果
+- 请补充更多详情图以展示商品细节</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PROD009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>损坏图片测试商品</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>- 主图: 主图文件损坏无法打开: cannot identify image file 'sample_data\\images\\PROD009_main.jpg'
+- detail_images: 缺少商品详情图</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>- 请重新上传或修复该图片
+- 请在 images 目录下添加 PROD009_detail_1.jpg, PROD009_detail_2.jpg 等详情图</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PROD010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>大文件图片测试商品</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>- detail_images: 缺少商品详情图</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>- 请在 images 目录下添加 PROD010_detail_1.jpg, PROD010_detail_2.jpg 等详情图</t>
         </is>
       </c>
     </row>
